--- a/test-cases/Zawaaj_Tests_EndUser.xlsx
+++ b/test-cases/Zawaaj_Tests_EndUser.xlsx
@@ -1670,17 +1670,18 @@
         <v>Registration</v>
       </c>
       <c r="E5" t="str">
-        <v>Complete child registration — independent</v>
+        <v>Form state preserved if user opens T&amp;C mid-wizard</v>
       </c>
       <c r="F5" t="str">
-        <v>Valid email; no existing account</v>
+        <v>In the middle of completing the wizard (e.g. personal details filled in)</v>
       </c>
       <c r="G5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Complete all 8 steps with guardian details
-2. Submit</v>
+        <v xml:space="preserve">1. Fill in steps 1–2 of the child registration form
+2. Click the Terms of Use link
+3. Close that tab and return to the form</v>
       </c>
       <c r="H5" t="str">
-        <v>Auth user created; new family account created; profile created; redirect to /pending</v>
+        <v>All previously entered fields are still filled in — no data has been lost</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -1692,7 +1693,7 @@
         <v/>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>CHD-B-005</v>
       </c>
@@ -1703,19 +1704,20 @@
         <v/>
       </c>
       <c r="D6" t="str">
-        <v>Post-registration</v>
+        <v>Registration</v>
       </c>
       <c r="E6" t="str">
-        <v>Pending state after child direct registration</v>
+        <v>Complete child registration — independent</v>
       </c>
       <c r="F6" t="str">
-        <v>Just completed child Path B registration</v>
-      </c>
-      <c r="G6" t="str">
-        <v>1. Check /pending</v>
+        <v>Valid email; no existing account</v>
+      </c>
+      <c r="G6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Complete all steps with guardian details
+2. Submit</v>
       </c>
       <c r="H6" t="str">
-        <v>"Application submitted" message with clock icon; no email verification pending state</v>
+        <v>Auth user created; new family account created with status=active; profile created with status=pending</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -1732,25 +1734,25 @@
         <v>CHD-B-006</v>
       </c>
       <c r="B7" t="str">
-        <v>Super Admin</v>
+        <v>Self</v>
       </c>
       <c r="C7" t="str">
         <v/>
       </c>
       <c r="D7" t="str">
-        <v>Family account</v>
+        <v>Post-registration</v>
       </c>
       <c r="E7" t="str">
-        <v>New family account created for independent child</v>
+        <v>Email verification screen after child direct registration</v>
       </c>
       <c r="F7" t="str">
-        <v>Completed Path B direct registration</v>
+        <v>Just completed child Path B registration</v>
       </c>
       <c r="G7" t="str">
-        <v>1. In admin /admin/families, search by contact email or name</v>
+        <v>1. Review the screen shown after clicking Submit</v>
       </c>
       <c r="H7" t="str">
-        <v>New family account exists with registration_path = child_direct</v>
+        <v>Envelope illustration shown with contact email; "Resend email" button available</v>
       </c>
       <c r="I7" t="str">
         <v/>
